--- a/supplemental/csi_surface_roughness/csi_surface_roughness_summary.xlsx
+++ b/supplemental/csi_surface_roughness/csi_surface_roughness_summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakep\Documents\Optics_local\UofA\bsdf-tools\supplemental\csi_surface_roughness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560AFC17-EEE6-490A-97AA-E33433C278AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B285842-ED3A-48C3-8E80-124961217A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,9 +134,6 @@
     <t>*which mount is A,B,C is not recorded; the purpose is just to average across the different mounts.</t>
   </si>
   <si>
-    <t>*tried various CSI settings, but none could register a measurement.</t>
-  </si>
-  <si>
     <t>**Vacuum Black on Glass</t>
   </si>
   <si>
@@ -162,6 +159,9 @@
   </si>
   <si>
     <t>SUMMARY:</t>
+  </si>
+  <si>
+    <t>**tried various CSI settings, but none could register a measurement.</t>
   </si>
 </sst>
 </file>
@@ -460,6 +460,13 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -469,13 +476,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,12 +790,12 @@
     </row>
     <row r="2" spans="2:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R2" s="19"/>
       <c r="S2" s="10"/>
       <c r="T2" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AG2" s="19"/>
     </row>
@@ -804,39 +804,39 @@
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="10" t="s">
-        <v>36</v>
-      </c>
       <c r="R3" s="19"/>
-      <c r="T3" s="27" t="s">
+      <c r="T3" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="28"/>
-      <c r="Y3" s="29"/>
-      <c r="Z3" s="27" t="s">
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
+      <c r="X3" s="35"/>
+      <c r="Y3" s="36"/>
+      <c r="Z3" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-      <c r="AE3" s="29"/>
-      <c r="AG3" s="36"/>
+      <c r="AA3" s="35"/>
+      <c r="AB3" s="35"/>
+      <c r="AC3" s="35"/>
+      <c r="AD3" s="35"/>
+      <c r="AE3" s="36"/>
+      <c r="AG3" s="33"/>
     </row>
     <row r="4" spans="2:33" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="3" t="s">
@@ -868,7 +868,7 @@
         <v>14</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="10"/>
       <c r="R4" s="19"/>
@@ -919,15 +919,15 @@
       </c>
       <c r="D5" s="12"/>
       <c r="E5" s="15">
-        <f>AVERAGE(T5:Y5)</f>
+        <f t="shared" ref="E5:E13" si="0">AVERAGE(T5:Y5)</f>
         <v>2.0246666666666666</v>
       </c>
       <c r="F5" s="6">
-        <f>AVERAGE(Z5:AE5)</f>
+        <f t="shared" ref="F5:F13" si="1">AVERAGE(Z5:AE5)</f>
         <v>13.995333333333333</v>
       </c>
       <c r="G5" s="11"/>
-      <c r="H5" s="30">
+      <c r="H5" s="27">
         <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
@@ -942,15 +942,15 @@
       <c r="L5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M5" s="33">
+      <c r="M5" s="30">
         <v>3</v>
       </c>
       <c r="N5" s="11"/>
-      <c r="O5" s="30">
+      <c r="O5" s="27">
         <v>3</v>
       </c>
-      <c r="P5" s="33">
-        <f t="shared" ref="P5:P7" si="0">M5*O5</f>
+      <c r="P5" s="30">
+        <f t="shared" ref="P5:P7" si="2">M5*O5</f>
         <v>9</v>
       </c>
       <c r="Q5" s="11"/>
@@ -991,15 +991,15 @@
       </c>
       <c r="D6" s="12"/>
       <c r="E6" s="15">
-        <f>AVERAGE(T6:Y6)</f>
+        <f t="shared" si="0"/>
         <v>1.222</v>
       </c>
       <c r="F6" s="6">
-        <f>AVERAGE(Z6:AE6)</f>
+        <f t="shared" si="1"/>
         <v>10.475</v>
       </c>
       <c r="G6" s="11"/>
-      <c r="H6" s="31">
+      <c r="H6" s="28">
         <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -1014,15 +1014,15 @@
       <c r="L6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="31">
         <v>3</v>
       </c>
       <c r="N6" s="11"/>
-      <c r="O6" s="31">
+      <c r="O6" s="28">
         <v>2</v>
       </c>
-      <c r="P6" s="34">
-        <f t="shared" si="0"/>
+      <c r="P6" s="31">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="Q6" s="11"/>
@@ -1059,15 +1059,15 @@
       </c>
       <c r="D7" s="12"/>
       <c r="E7" s="15">
-        <f>AVERAGE(T7:Y7)</f>
+        <f t="shared" si="0"/>
         <v>1.6339999999999999</v>
       </c>
       <c r="F7" s="6">
-        <f>AVERAGE(Z7:AE7)</f>
+        <f t="shared" si="1"/>
         <v>12.502500000000001</v>
       </c>
       <c r="G7" s="11"/>
-      <c r="H7" s="31">
+      <c r="H7" s="28">
         <v>20</v>
       </c>
       <c r="I7" s="1" t="s">
@@ -1082,15 +1082,15 @@
       <c r="L7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M7" s="34">
+      <c r="M7" s="31">
         <v>3</v>
       </c>
       <c r="N7" s="11"/>
-      <c r="O7" s="31">
+      <c r="O7" s="28">
         <v>2</v>
       </c>
-      <c r="P7" s="34">
-        <f t="shared" si="0"/>
+      <c r="P7" s="31">
+        <f t="shared" si="2"/>
         <v>6</v>
       </c>
       <c r="Q7" s="11"/>
@@ -1120,22 +1120,22 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B8" s="21" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="22">
         <v>46080</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="15">
-        <f>AVERAGE(T8:Y8)</f>
+        <f t="shared" si="0"/>
         <v>3.4919999999999995</v>
       </c>
       <c r="F8" s="6">
-        <f>AVERAGE(Z8:AE8)</f>
+        <f t="shared" si="1"/>
         <v>23.989833333333333</v>
       </c>
       <c r="G8" s="11"/>
-      <c r="H8" s="31">
+      <c r="H8" s="28">
         <v>40</v>
       </c>
       <c r="I8" s="1" t="s">
@@ -1150,14 +1150,14 @@
       <c r="L8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M8" s="34">
+      <c r="M8" s="31">
         <v>3</v>
       </c>
       <c r="N8" s="11"/>
-      <c r="O8" s="31">
+      <c r="O8" s="28">
         <v>6</v>
       </c>
-      <c r="P8" s="34">
+      <c r="P8" s="31">
         <f>M8*O8</f>
         <v>18</v>
       </c>
@@ -1211,15 +1211,15 @@
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="15">
-        <f>AVERAGE(T9:Y9)</f>
+        <f t="shared" si="0"/>
         <v>1.6526666666666667</v>
       </c>
       <c r="F9" s="6">
-        <f>AVERAGE(Z9:AE9)</f>
+        <f t="shared" si="1"/>
         <v>11.513666666666666</v>
       </c>
       <c r="G9" s="11"/>
-      <c r="H9" s="31">
+      <c r="H9" s="28">
         <v>20</v>
       </c>
       <c r="I9" s="1" t="s">
@@ -1234,15 +1234,15 @@
       <c r="L9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M9" s="34">
+      <c r="M9" s="31">
         <v>3</v>
       </c>
       <c r="N9" s="11"/>
-      <c r="O9" s="31">
+      <c r="O9" s="28">
         <v>3</v>
       </c>
-      <c r="P9" s="34">
-        <f t="shared" ref="P9" si="1">M9*O9</f>
+      <c r="P9" s="31">
+        <f t="shared" ref="P9" si="3">M9*O9</f>
         <v>9</v>
       </c>
       <c r="Q9" s="11"/>
@@ -1283,15 +1283,15 @@
       </c>
       <c r="D10" s="12"/>
       <c r="E10" s="15">
-        <f>AVERAGE(T10:Y10)</f>
+        <f t="shared" si="0"/>
         <v>4.4770000000000003</v>
       </c>
       <c r="F10" s="6">
-        <f>AVERAGE(Z10:AE10)</f>
+        <f t="shared" si="1"/>
         <v>29.651</v>
       </c>
       <c r="G10" s="11"/>
-      <c r="H10" s="31">
+      <c r="H10" s="28">
         <v>40</v>
       </c>
       <c r="I10" s="1" t="s">
@@ -1306,14 +1306,14 @@
       <c r="L10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="34">
+      <c r="M10" s="31">
         <v>3</v>
       </c>
       <c r="N10" s="11"/>
-      <c r="O10" s="31">
+      <c r="O10" s="28">
         <v>2</v>
       </c>
-      <c r="P10" s="34">
+      <c r="P10" s="31">
         <f>M10*O10</f>
         <v>6</v>
       </c>
@@ -1351,15 +1351,15 @@
       </c>
       <c r="D11" s="12"/>
       <c r="E11" s="15">
-        <f>AVERAGE(T11:Y11)</f>
+        <f t="shared" si="0"/>
         <v>16.506999999999998</v>
       </c>
       <c r="F11" s="6">
-        <f>AVERAGE(Z11:AE11)</f>
+        <f t="shared" si="1"/>
         <v>115.58199999999999</v>
       </c>
       <c r="G11" s="11"/>
-      <c r="H11" s="31">
+      <c r="H11" s="28">
         <v>145</v>
       </c>
       <c r="I11" s="1" t="s">
@@ -1374,15 +1374,15 @@
       <c r="L11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="34">
+      <c r="M11" s="31">
         <v>3</v>
       </c>
       <c r="N11" s="11"/>
-      <c r="O11" s="31">
+      <c r="O11" s="28">
         <v>2</v>
       </c>
-      <c r="P11" s="34">
-        <f t="shared" ref="P11" si="2">M11*O11</f>
+      <c r="P11" s="31">
+        <f t="shared" ref="P11" si="4">M11*O11</f>
         <v>6</v>
       </c>
       <c r="Q11" s="11"/>
@@ -1419,15 +1419,15 @@
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="15">
-        <f>AVERAGE(T12:Y12)</f>
+        <f t="shared" si="0"/>
         <v>1.208</v>
       </c>
       <c r="F12" s="6">
-        <f>AVERAGE(Z12:AE12)</f>
+        <f t="shared" si="1"/>
         <v>10.303000000000001</v>
       </c>
       <c r="G12" s="11"/>
-      <c r="H12" s="31">
+      <c r="H12" s="28">
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
@@ -1442,14 +1442,14 @@
       <c r="L12" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="31">
         <v>3</v>
       </c>
       <c r="N12" s="11"/>
-      <c r="O12" s="31">
+      <c r="O12" s="28">
         <v>1</v>
       </c>
-      <c r="P12" s="34">
+      <c r="P12" s="31">
         <f>M12*O12</f>
         <v>3</v>
       </c>
@@ -1483,15 +1483,15 @@
       </c>
       <c r="D13" s="12"/>
       <c r="E13" s="15">
-        <f>AVERAGE(T13:Y13)</f>
+        <f t="shared" si="0"/>
         <v>1.0649999999999999</v>
       </c>
       <c r="F13" s="6">
-        <f>AVERAGE(Z13:AE13)</f>
+        <f t="shared" si="1"/>
         <v>11.181000000000001</v>
       </c>
       <c r="G13" s="11"/>
-      <c r="H13" s="31">
+      <c r="H13" s="28">
         <v>20</v>
       </c>
       <c r="I13" s="1" t="s">
@@ -1506,15 +1506,15 @@
       <c r="L13" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="31">
         <v>3</v>
       </c>
       <c r="N13" s="11"/>
-      <c r="O13" s="31">
+      <c r="O13" s="28">
         <v>2</v>
       </c>
-      <c r="P13" s="34">
-        <f t="shared" ref="P13" si="3">M13*O13</f>
+      <c r="P13" s="31">
+        <f t="shared" ref="P13" si="5">M13*O13</f>
         <v>6</v>
       </c>
       <c r="Q13" s="11"/>
@@ -1544,7 +1544,7 @@
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B14" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="22">
         <v>46080</v>
@@ -1557,7 +1557,7 @@
         <v>12</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="31" t="s">
+      <c r="H14" s="28" t="s">
         <v>12</v>
       </c>
       <c r="I14" s="1" t="s">
@@ -1572,14 +1572,14 @@
       <c r="L14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M14" s="34" t="s">
+      <c r="M14" s="31" t="s">
         <v>12</v>
       </c>
       <c r="N14" s="11"/>
-      <c r="O14" s="31" t="s">
+      <c r="O14" s="28" t="s">
         <v>12</v>
       </c>
-      <c r="P14" s="34" t="s">
+      <c r="P14" s="31" t="s">
         <v>12</v>
       </c>
       <c r="Q14" s="11"/>
@@ -1620,7 +1620,7 @@
         <v>6.6984999999999992</v>
       </c>
       <c r="G15" s="11"/>
-      <c r="H15" s="32">
+      <c r="H15" s="29">
         <v>10</v>
       </c>
       <c r="I15" s="8" t="s">
@@ -1635,15 +1635,15 @@
       <c r="L15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="35">
+      <c r="M15" s="32">
         <v>3</v>
       </c>
       <c r="N15" s="11"/>
-      <c r="O15" s="32">
+      <c r="O15" s="29">
         <v>2</v>
       </c>
-      <c r="P15" s="35">
-        <f t="shared" ref="P15" si="4">M15*O15</f>
+      <c r="P15" s="32">
+        <f t="shared" ref="P15" si="6">M15*O15</f>
         <v>6</v>
       </c>
       <c r="Q15" s="11"/>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B18" s="12" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>

--- a/supplemental/csi_surface_roughness/csi_surface_roughness_summary.xlsx
+++ b/supplemental/csi_surface_roughness/csi_surface_roughness_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakep\Documents\Optics_local\UofA\bsdf-tools\supplemental\csi_surface_roughness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B285842-ED3A-48C3-8E80-124961217A8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D0A130-C5F0-4E57-8BC4-E93001AC173A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3468" yWindow="3720" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>DEEP SPACE BLACK - Full Spectrum Basic</t>
   </si>
   <si>
-    <t>Aeroglaze 9924 Primer with Aeroglaze 2307 Black</t>
-  </si>
-  <si>
     <t>Vacuum Black on Aluminum</t>
   </si>
   <si>
@@ -162,6 +159,9 @@
   </si>
   <si>
     <t>**tried various CSI settings, but none could register a measurement.</t>
+  </si>
+  <si>
+    <t>Aeroglaze 9924 Primer with Aeroglaze Z307 Black</t>
   </si>
 </sst>
 </file>
@@ -790,12 +790,12 @@
     </row>
     <row r="2" spans="2:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B2" s="10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="R2" s="19"/>
       <c r="S2" s="10"/>
       <c r="T2" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG2" s="19"/>
     </row>
@@ -804,17 +804,17 @@
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
       <c r="E3" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="10" t="s">
         <v>34</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>35</v>
       </c>
       <c r="R3" s="19"/>
       <c r="T3" s="34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="U3" s="35"/>
       <c r="V3" s="35"/>
@@ -822,7 +822,7 @@
       <c r="X3" s="35"/>
       <c r="Y3" s="36"/>
       <c r="Z3" s="34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA3" s="35"/>
       <c r="AB3" s="35"/>
@@ -833,86 +833,86 @@
     </row>
     <row r="4" spans="2:33" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4" s="10"/>
       <c r="E4" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="N4" s="10"/>
       <c r="O4" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Q4" s="10"/>
       <c r="R4" s="19"/>
       <c r="T4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="U4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="V4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="W4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="X4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="X4" s="17" t="s">
+      <c r="Y4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="Y4" s="18" t="s">
-        <v>30</v>
-      </c>
       <c r="Z4" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA4" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AA4" s="17" t="s">
+      <c r="AB4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="AB4" s="17" t="s">
+      <c r="AC4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="AC4" s="17" t="s">
+      <c r="AD4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="AD4" s="17" t="s">
+      <c r="AE4" s="18" t="s">
         <v>29</v>
-      </c>
-      <c r="AE4" s="18" t="s">
-        <v>30</v>
       </c>
       <c r="AG4" s="19"/>
     </row>
     <row r="5" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B5" s="25" t="s">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C5" s="26">
         <v>46080</v>
@@ -931,16 +931,16 @@
         <v>20</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M5" s="30">
         <v>3</v>
@@ -984,7 +984,7 @@
     </row>
     <row r="6" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B6" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="22">
         <v>46080</v>
@@ -1003,16 +1003,16 @@
         <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M6" s="31">
         <v>3</v>
@@ -1052,7 +1052,7 @@
     </row>
     <row r="7" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B7" s="21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" s="22">
         <v>46080</v>
@@ -1071,16 +1071,16 @@
         <v>20</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M7" s="31">
         <v>3</v>
@@ -1120,7 +1120,7 @@
     </row>
     <row r="8" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B8" s="21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="22">
         <v>46080</v>
@@ -1139,16 +1139,16 @@
         <v>40</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M8" s="31">
         <v>3</v>
@@ -1204,7 +1204,7 @@
     </row>
     <row r="9" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B9" s="21" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C9" s="22">
         <v>46080</v>
@@ -1223,16 +1223,16 @@
         <v>20</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" s="31">
         <v>3</v>
@@ -1295,16 +1295,16 @@
         <v>40</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M10" s="31">
         <v>3</v>
@@ -1344,7 +1344,7 @@
     </row>
     <row r="11" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B11" s="21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" s="22">
         <v>46080</v>
@@ -1363,16 +1363,16 @@
         <v>145</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M11" s="31">
         <v>3</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="12" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B12" s="21" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="22">
         <v>45898</v>
@@ -1431,16 +1431,16 @@
         <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M12" s="31">
         <v>3</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="13" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B13" s="21" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" s="22">
         <v>46080</v>
@@ -1495,16 +1495,16 @@
         <v>20</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M13" s="31">
         <v>3</v>
@@ -1544,49 +1544,49 @@
     </row>
     <row r="14" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B14" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" s="22">
         <v>46080</v>
       </c>
       <c r="D14" s="12"/>
       <c r="E14" s="15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M14" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="N14" s="11"/>
       <c r="O14" s="28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="P14" s="31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Q14" s="11"/>
       <c r="R14" s="20"/>
       <c r="S14" s="12"/>
       <c r="T14" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1"/>
@@ -1594,7 +1594,7 @@
       <c r="X14" s="1"/>
       <c r="Y14" s="7"/>
       <c r="Z14" s="13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA14" s="1"/>
       <c r="AB14" s="1"/>
@@ -1605,7 +1605,7 @@
     </row>
     <row r="15" spans="2:33" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B15" s="23" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" s="24">
         <v>46080</v>
@@ -1624,16 +1624,16 @@
         <v>10</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K15" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M15" s="32">
         <v>3</v>
@@ -1694,7 +1694,7 @@
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="N17" s="10"/>
       <c r="R17" s="19"/>
@@ -1702,7 +1702,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.3">
       <c r="B18" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C18" s="12"/>
       <c r="D18" s="12"/>
